--- a/backend/app/static/templates/sample_import_template.xlsx
+++ b/backend/app/static/templates/sample_import_template.xlsx
@@ -425,29 +425,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
-    <col width="7" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
+    <col width="50" customWidth="1" min="19" max="19"/>
+    <col width="50" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="17" customWidth="1" min="22" max="22"/>
     <col width="15" customWidth="1" min="23" max="23"/>
@@ -460,11 +460,11 @@
     <col width="17" customWidth="1" min="30" max="30"/>
     <col width="11" customWidth="1" min="31" max="31"/>
     <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="9" customWidth="1" min="33" max="33"/>
-    <col width="10" customWidth="1" min="34" max="34"/>
-    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="19" customWidth="1" min="35" max="35"/>
     <col width="13" customWidth="1" min="36" max="36"/>
-    <col width="20" customWidth="1" min="37" max="37"/>
+    <col width="50" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -838,6 +838,173 @@
       <c r="AK2" t="inlineStr">
         <is>
           <t>Thông tin sản phẩm</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A746204251298a188b0038</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B0038</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Việt Nam</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SHTDC</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Giày Tây Oxford Nam Da Thật Mũi Nhọn Chiều Cao Đế Khoảng 3cm Màu Đen, Nâu</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Giày Tây Oxford Nam Da Thật là một lựa chọn hoàn hảo thuộc dòng Giày dép Nam, đặc biệt là Giày tây Nam.</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>2260000</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>giày tây nam shtdc</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>nam G05</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>giày dép nam G04</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>giày dép nam G06</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>90</v>
+      </c>
+      <c r="M3" t="n">
+        <v>99</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>["37", "38", "39", "40", "41", "42", "43", "44", "45", "46"]</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>[{"name": "Màu đen", "img": "https://img.alicdn.com/img/ibank/O1CN01q0djJj2LWec6Kkpij_!!3577759700-0-cib.jpg"}, {"name": "Nâu cổ điển", "img": "https://img.alicdn.com/img/ibank/O1CN01bsGpk22LWecAoruAN_!!3577759700-0-cib.jpg"}]</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>["https://img.alicdn.com/img/ibank/O1CN017R3Bf62LWeizFVWog_!!3577759700-0-cib.jpg"]</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>["https://188.com.vn/uploads/size-san-pham/size%20gi%C3%A0y%20nam.jpg"]</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>https://188.com.vn/product/B0038</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>https://cloud.video.taobao.com/play/u/3577759700/p/1/e/6/t/1/375400310804.mp4</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>//img.alicdn.com/img/ibank/O1CN017R3Bf62LWeizFVWog_!!3577759700-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>100</v>
+      </c>
+      <c r="V3" t="n">
+        <v>81</v>
+      </c>
+      <c r="W3" t="n">
+        <v>72</v>
+      </c>
+      <c r="X3" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Giày dép Nam</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Giày tây Nam</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Giày Oxford Nam</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Da bò</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Dây buộc</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Đen, Xanh</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Lễ cưới, dự tiệc</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Nâng đế, tăng cao</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>{"product_info": {"sku": "B0038", "name": "Giày Tây Oxford Nam", "brand": "SHTDC", "origin": "Việt Nam", "category": {"level_1": "Giày dép Nam", "level_2": "Giày tây Nam", "level_3": "Giày Oxford Nam"}}, "specifications": {"upper_material": "Da bò", "lining_material": "Lót da", "outsole_material": "Cao su", "weight_grams": 500}, "variants": {"colors": ["Đen", "Nâu"], "sizes": [38, 39, 40, 41, 42, 43, 44, 45]}, "target_audience": {"gender": "Nam", "age_range": "18-40", "style": "Công sở"}, "market_info": {"season": "Quanh năm", "lead_time_days": "1-3 ngày", "main_sales_regions": ["Việt Nam"]}}</t>
         </is>
       </c>
     </row>

--- a/backend/app/static/templates/sample_import_template.xlsx
+++ b/backend/app/static/templates/sample_import_template.xlsx
@@ -430,13 +430,13 @@
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
@@ -852,16 +852,8 @@
           <t>B0038</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Việt Nam</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SHTDC</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Giày Tây Oxford Nam Da Thật Mũi Nhọn Chiều Cao Đế Khoảng 3cm Màu Đen, Nâu</t>
@@ -882,7 +874,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>nam G05</t>
+          <t>Dây buộc</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -937,19 +929,19 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="V3" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="W3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z3" t="n">
         <v>500</v>

--- a/backend/app/static/templates/sample_import_template.xlsx
+++ b/backend/app/static/templates/sample_import_template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -465,6 +465,8 @@
     <col width="19" customWidth="1" min="35" max="35"/>
     <col width="13" customWidth="1" min="36" max="36"/>
     <col width="50" customWidth="1" min="37" max="37"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -653,6 +655,16 @@
           <t>product_info</t>
         </is>
       </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>chinese_name</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>shop_name_chinese</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -840,6 +852,16 @@
           <t>Thông tin sản phẩm</t>
         </is>
       </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Tên tiếng trung</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Shop Trung Quốc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -929,19 +951,19 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="V3" t="n">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="W3" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="X3" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="Y3" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="Z3" t="n">
         <v>500</v>
@@ -997,6 +1019,16 @@
       <c r="AK3" t="inlineStr">
         <is>
           <t>{"product_info": {"sku": "B0038", "name": "Giày Tây Oxford Nam", "brand": "SHTDC", "origin": "Việt Nam", "category": {"level_1": "Giày dép Nam", "level_2": "Giày tây Nam", "level_3": "Giày Oxford Nam"}}, "specifications": {"upper_material": "Da bò", "lining_material": "Lót da", "outsole_material": "Cao su", "weight_grams": 500}, "variants": {"colors": ["Đen", "Nâu"], "sizes": [38, 39, 40, 41, 42, 43, 44, 45]}, "target_audience": {"gender": "Nam", "age_range": "18-40", "style": "Công sở"}, "market_info": {"season": "Quanh năm", "lead_time_days": "1-3 ngày", "main_sales_regions": ["Việt Nam"]}}</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>商务正装皮鞋男牛津鞋真皮尖头增高</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>示例义乌商行</t>
         </is>
       </c>
     </row>

--- a/backend/app/static/templates/sample_import_template.xlsx
+++ b/backend/app/static/templates/sample_import_template.xlsx
@@ -435,10 +435,10 @@
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
@@ -889,26 +889,10 @@
       <c r="G3" t="n">
         <v>2260000</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>giày tây nam shtdc</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Dây buộc</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>giày dép nam G04</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>giày dép nam G06</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>90</v>
       </c>
@@ -951,19 +935,19 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="V3" t="n">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="W3" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="X3" t="n">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.99</v>
+        <v>4.92</v>
       </c>
       <c r="Z3" t="n">
         <v>500</v>

--- a/backend/app/static/templates/sample_import_template.xlsx
+++ b/backend/app/static/templates/sample_import_template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM3"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -467,6 +467,7 @@
     <col width="50" customWidth="1" min="37" max="37"/>
     <col width="18" customWidth="1" min="38" max="38"/>
     <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="38" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -665,6 +666,11 @@
           <t>shop_name_chinese</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>listed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -860,6 +866,11 @@
       <c r="AM2" t="inlineStr">
         <is>
           <t>Shop Trung Quốc</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>Trong danh sách (1=import, 0=xóa DB)</t>
         </is>
       </c>
     </row>
@@ -935,19 +946,19 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="V3" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="W3" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="X3" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.92</v>
+        <v>4.84</v>
       </c>
       <c r="Z3" t="n">
         <v>500</v>
@@ -1014,6 +1025,9 @@
         <is>
           <t>示例义乌商行</t>
         </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
